--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>127129149</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>127129149</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>127129149</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>127129149</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1174,6 +1174,981 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129705717</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>655010</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6648264</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129705704</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>654964</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6648195</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129705719</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>654963</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6648079</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129705699</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>654915</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6648237</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129705722</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100957</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>654913</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6648264</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129705686</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>654909</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6648322</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129705695</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>654906</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6648271</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129705694</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>654963</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6648079</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129705685</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>654899</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6648321</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129705700</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>654899</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6648321</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>129705704</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>129705699</v>
       </c>
       <c r="B9" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129705722</v>
       </c>
       <c r="B10" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>129705686</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129705695</v>
       </c>
       <c r="B12" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>129705694</v>
       </c>
       <c r="B13" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129705685</v>
       </c>
       <c r="B14" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129705700</v>
       </c>
       <c r="B15" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1176,32 +1176,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129705717</v>
+        <v>129705704</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655010</v>
+        <v>654964</v>
       </c>
       <c r="R6" t="n">
-        <v>6648264</v>
+        <v>6648195</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1247,6 +1247,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,32 +1278,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129705704</v>
+        <v>129705717</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>5177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1308,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654964</v>
+        <v>655010</v>
       </c>
       <c r="R7" t="n">
-        <v>6648195</v>
+        <v>6648264</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1344,11 +1349,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1475,7 +1475,7 @@
         <v>129705699</v>
       </c>
       <c r="B9" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129705722</v>
       </c>
       <c r="B10" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129705685</v>
       </c>
       <c r="B14" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129705700</v>
       </c>
       <c r="B15" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1176,32 +1176,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129705704</v>
+        <v>129705717</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654964</v>
+        <v>655010</v>
       </c>
       <c r="R6" t="n">
-        <v>6648195</v>
+        <v>6648264</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1247,11 +1247,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,32 +1273,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129705717</v>
+        <v>129705704</v>
       </c>
       <c r="B7" t="n">
-        <v>5177</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655010</v>
+        <v>654964</v>
       </c>
       <c r="R7" t="n">
-        <v>6648264</v>
+        <v>6648195</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1349,6 +1344,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>129705704</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>129705699</v>
       </c>
       <c r="B9" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129705722</v>
       </c>
       <c r="B10" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129705685</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129705700</v>
       </c>
       <c r="B15" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>129705704</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>129705699</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129705722</v>
       </c>
       <c r="B10" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129705685</v>
       </c>
       <c r="B14" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129705700</v>
       </c>
       <c r="B15" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>129705704</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129705722</v>
       </c>
       <c r="B10" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>129705704</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>129705699</v>
       </c>
       <c r="B9" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129705722</v>
       </c>
       <c r="B10" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>129705686</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129705695</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>129705694</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129705685</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129705700</v>
       </c>
       <c r="B15" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>129705704</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>129705699</v>
       </c>
       <c r="B9" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129705722</v>
       </c>
       <c r="B10" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>129705686</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129705695</v>
       </c>
       <c r="B12" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>129705694</v>
       </c>
       <c r="B13" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129705685</v>
       </c>
       <c r="B14" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129705700</v>
       </c>
       <c r="B15" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>129705704</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>129705699</v>
       </c>
       <c r="B9" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129705722</v>
       </c>
       <c r="B10" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129705685</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129705700</v>
       </c>
       <c r="B15" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>129705704</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>129705699</v>
       </c>
       <c r="B9" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129705722</v>
       </c>
       <c r="B10" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>129705686</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129705685</v>
       </c>
       <c r="B14" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129705700</v>
       </c>
       <c r="B15" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -835,7 +835,7 @@
         <v>127128806</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127129103</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>127129149</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25608-2025 artfynd.xlsx
+++ b/artfynd/A 25608-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,68 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>77318615</v>
+        <v>129705685</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tomta, 1,2 km SV-ut, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655015.1692252198</v>
+        <v>654899</v>
       </c>
       <c r="R2" t="n">
-        <v>6648250.852375326</v>
+        <v>6648321</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Den vita märgen är KOH-negativ och bålens undersida ljusbrun och kal.</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,100 +754,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128806</v>
+        <v>129705699</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654932</v>
+        <v>654915</v>
       </c>
       <c r="R3" t="n">
-        <v>6648269</v>
+        <v>6648237</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,69 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127129103</v>
+        <v>129705700</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654895</v>
+        <v>654899</v>
       </c>
       <c r="R4" t="n">
-        <v>6648227</v>
+        <v>6648321</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,65 +954,75 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127129149</v>
+        <v>77318615</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, 1,2 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654895</v>
+        <v>655015</v>
       </c>
       <c r="R5" t="n">
-        <v>6648227</v>
+        <v>6648251</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,22 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Den vita märgen är KOH-negativ och bålens undersida ljusbrun och kal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,28 +1065,53 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129705717</v>
+        <v>127128701</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,37 +1119,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655010</v>
+        <v>654896</v>
       </c>
       <c r="R6" t="n">
-        <v>6648264</v>
+        <v>6648313</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,12 +1178,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,60 +1208,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129705704</v>
+        <v>127129149</v>
       </c>
       <c r="B7" t="n">
-        <v>98820</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654964</v>
+        <v>654895</v>
       </c>
       <c r="R7" t="n">
-        <v>6648195</v>
+        <v>6648227</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,17 +1290,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>7 buketter</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129705719</v>
+        <v>129705694</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1472,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129705699</v>
+        <v>129705695</v>
       </c>
       <c r="B9" t="n">
-        <v>92081</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654915</v>
+        <v>654906</v>
       </c>
       <c r="R9" t="n">
-        <v>6648237</v>
+        <v>6648271</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1569,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129705722</v>
+        <v>129705717</v>
       </c>
       <c r="B10" t="n">
-        <v>101009</v>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,7 +1561,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654913</v>
+        <v>655010</v>
       </c>
       <c r="R10" t="n">
         <v>6648264</v>
@@ -1666,32 +1623,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129705686</v>
+        <v>129705719</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654909</v>
+        <v>654963</v>
       </c>
       <c r="R11" t="n">
-        <v>6648322</v>
+        <v>6648079</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1763,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129705695</v>
+        <v>129705686</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654906</v>
+        <v>654909</v>
       </c>
       <c r="R12" t="n">
-        <v>6648271</v>
+        <v>6648322</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,27 +1817,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129705694</v>
+        <v>127128688</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>5199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1889,19 +1846,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654963</v>
+        <v>654874</v>
       </c>
       <c r="R13" t="n">
-        <v>6648079</v>
+        <v>6648329</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1925,12 +1887,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,60 +1917,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129705685</v>
+        <v>127128806</v>
       </c>
       <c r="B14" t="n">
-        <v>91628</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654899</v>
+        <v>654932</v>
       </c>
       <c r="R14" t="n">
-        <v>6648321</v>
+        <v>6648269</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2022,12 +2003,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,22 +2033,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129705700</v>
+        <v>127129103</v>
       </c>
       <c r="B15" t="n">
-        <v>92081</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,37 +2056,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654899</v>
+        <v>654895</v>
       </c>
       <c r="R15" t="n">
-        <v>6648321</v>
+        <v>6648227</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2119,12 +2119,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2139,15 +2149,434 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129705704</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>654964</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6648195</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131735014</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kasimirshagen Nordost, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>654887</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6648309</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131735015</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stamsäng Nordväst, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>654866</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6648302</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129705722</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>654913</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6648264</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
